--- a/public/assets/excel_router_solution.xlsx
+++ b/public/assets/excel_router_solution.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcc\git\informatikgarten.ch\content\3 Computer &amp; Netzwerke\2 Netzwerke und das Internet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcc\git\informatikgarten.ch\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC6E85E-6066-4F05-B6F1-4C57F0F70A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F6059B-5C28-4A34-A909-D724F5B28683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="14220" activeTab="2" xr2:uid="{8B4C5CB2-983E-4FDC-89E4-8A1111F2665D}"/>
   </bookViews>
   <sheets>
     <sheet name="Einstieg" sheetId="1" r:id="rId1"/>
-    <sheet name="Binäre Erklärung" sheetId="3" r:id="rId2"/>
+    <sheet name="Binäre Erklärung" sheetId="6" r:id="rId2"/>
     <sheet name="IP-Router" sheetId="2" r:id="rId3"/>
+    <sheet name="Beispiele" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="97">
   <si>
     <t>Einstieg: Excel-Formeln</t>
   </si>
@@ -99,6 +100,9 @@
       </rPr>
       <t>gebrauchen, wie z.B. sum(). ACHTUNG: Excel übersetzt die Funktionen in andere Sprachen, also vielleicht heisst die Funktion bei Ihnen "summe()".</t>
     </r>
+  </si>
+  <si>
+    <t>Sie sind sicher einverstanden, dass die Formel des letzten Beispiels etwas unschön ist.</t>
   </si>
   <si>
     <r>
@@ -148,9 +152,6 @@
     </r>
   </si>
   <si>
-    <t>Sie sind sicher einverstanden, dass die Formel des letzten Beispiels etwas unschön ist.</t>
-  </si>
-  <si>
     <t>Hier nochmal dasselbe Beispiel einfacher geschrieben:</t>
   </si>
   <si>
@@ -158,54 +159,6 @@
   </si>
   <si>
     <t>Sie oben auf das "fx"-Symbol</t>
-  </si>
-  <si>
-    <t>Jetzt sind Sie dran!</t>
-  </si>
-  <si>
-    <t>Lösen Sie folgende Aufgaben</t>
-  </si>
-  <si>
-    <t>Inputs sind orange</t>
-  </si>
-  <si>
-    <t>Ihre Formel / das Ergebnis ist gelb</t>
-  </si>
-  <si>
-    <t>1.) Summieren Sie diesen ganzen Bereich:</t>
-  </si>
-  <si>
-    <t>2.) Finden Sie die kleinste Zahl mit der Funktion min()</t>
-  </si>
-  <si>
-    <t>3.) Dividieren Sie die erste Zahl durch die zweite mit deren Koordinaten:</t>
-  </si>
-  <si>
-    <t>Zwischenergebnisse sind hellblau</t>
-  </si>
-  <si>
-    <t>Zahlenbeispiel</t>
-  </si>
-  <si>
-    <t>12-5=</t>
-  </si>
-  <si>
-    <t>4.) Summieren Sie die Ergebnisse aller Substraktionen</t>
-  </si>
-  <si>
-    <t>5.) Nutzen Sie die Funktion if(), auf Deutsch wenn(), um die "Zahlen sind gleich!" auszugeben, wenn beide Zahlen gleich sind, oder "Zahlen sind ungleich!", wenn sie ungleich sind.</t>
-  </si>
-  <si>
-    <t>Subnet-Maske</t>
-  </si>
-  <si>
-    <t>Binär</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>6.) Überprüfen Sie, ob alle Zahlenpaare in den Zeilen gleich sind</t>
   </si>
   <si>
     <r>
@@ -249,10 +202,58 @@
     <t>und Zahlen sowie Formeln werden automatisch ergänzt.</t>
   </si>
   <si>
+    <t>Markieren Sie diese Zahlenreihen und erweitern Sie sie nach rechts:</t>
+  </si>
+  <si>
     <t>Markieren Sie diese Formeln und erweitern Sie sie nach rechts:</t>
   </si>
   <si>
-    <t>Markieren Sie diese Zahlenreihen und erweitern Sie sie nach rechts:</t>
+    <t>Jetzt sind Sie dran!</t>
+  </si>
+  <si>
+    <t>Lösen Sie folgende Aufgaben</t>
+  </si>
+  <si>
+    <t>Inputs sind orange</t>
+  </si>
+  <si>
+    <t>Ihre Formel / das Ergebnis ist gelb</t>
+  </si>
+  <si>
+    <t>Zwischenergebnisse sind hellblau</t>
+  </si>
+  <si>
+    <t>1.) Summieren Sie diesen ganzen Bereich:</t>
+  </si>
+  <si>
+    <t>2.) Finden Sie die kleinste Zahl mit der Funktion min()</t>
+  </si>
+  <si>
+    <t>3.) Dividieren Sie die erste Zahl durch die zweite mit deren Koordinaten:</t>
+  </si>
+  <si>
+    <t>4.) Summieren Sie die Ergebnisse aller Substraktionen</t>
+  </si>
+  <si>
+    <t>Zahlenbeispiel</t>
+  </si>
+  <si>
+    <t>12-5=</t>
+  </si>
+  <si>
+    <t>&lt;- Summe aller blauen Zwischenergebnisse</t>
+  </si>
+  <si>
+    <t>5.) Nutzen Sie die Funktion if(), auf Deutsch wenn(), um die "Zahlen sind gleich!" auszugeben, wenn beide Zahlen gleich sind, oder "Zahlen sind ungleich!", wenn sie ungleich sind.</t>
+  </si>
+  <si>
+    <t>6.) Überprüfen Sie, ob alle Zahlenpaare in den Zeilen gleich sind</t>
+  </si>
+  <si>
+    <t>Tipp: Sie können den Wert mit if() / wenn() auf 0 oder 1 setzen</t>
+  </si>
+  <si>
+    <t>Wie viele sind gleich?</t>
   </si>
   <si>
     <t>Sind alle gleich?</t>
@@ -261,34 +262,25 @@
     <t>Ja/Nein</t>
   </si>
   <si>
-    <t>Wie viele sind gleich?</t>
-  </si>
-  <si>
-    <t>&lt;- Summe aller blauen Zwischenergebnisse</t>
-  </si>
-  <si>
-    <t>Tipp: Sie können den Wert mit if() / wenn() auf 0 oder 1 setzen</t>
-  </si>
-  <si>
     <t>Tipp: Es gibt eine Funktion, um die Anzahl Reihen eines Bereichs zu zählen.</t>
   </si>
   <si>
-    <t>IP-Adresse</t>
+    <t>7.) Nutzen Sie die Funktion dec2bin() und bin2dec(), um Dezimalzahlen zu Binärzahlen umzurechen und wieder zurück.</t>
   </si>
   <si>
     <t>Dezimal</t>
   </si>
   <si>
-    <t>Netzwerk-Adr.</t>
+    <t>Binär</t>
   </si>
   <si>
     <t>101</t>
   </si>
   <si>
-    <t>7.) Nutzen Sie die Funktion dec2bin() und bin2dec(), um Dezimalzahlen zu Binärzahlen umzurechen und wieder zurück.</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.) dec2bin() hat ein Argument, um eine fixe Anzahl Ziffern auszugeben. </t>
+  </si>
+  <si>
+    <t>Können Sie folgende Zahlen in Binär ausgeben, sodass immer 8 Ziffern geschrieben werden?</t>
   </si>
   <si>
     <t>9.) Was ist die grösste Zahl, die mit 8 Binärziffern gespeichert werden kann?</t>
@@ -338,86 +330,215 @@
     <t>vor den Buchstaben oder die Zahl der Koordinaten, um diese fix zu halten.</t>
   </si>
   <si>
+    <t>Versuchen Sie ins blaue Feld eine Formel zu schreiben, die Sie dann einfach erweitern können, sodass ALLE Zahlen mit dem Multiplikator</t>
+  </si>
+  <si>
+    <t>im roten Feld multipliziert werden.</t>
+  </si>
+  <si>
     <t>Multiplikator</t>
   </si>
   <si>
-    <t>Versuchen Sie ins blaue Feld eine Formel zu schreiben, die Sie dann einfach erweitern können, sodass ALLE Zahlen mit dem Multiplikator</t>
-  </si>
-  <si>
-    <t>im roten Feld multipliziert werden.</t>
+    <t>Ändern Sie die Formel nun so ab, dass Sie das blaue Feld auf den ganzen gelben Bereich erweitern können und immernoch alles stimmt!</t>
   </si>
   <si>
     <t>Multiplikatoren</t>
   </si>
   <si>
-    <t>Ändern Sie die Formel nun so ab, dass Sie das blaue Feld auf den ganzen gelben Bereich erweitern können und immernoch alles stimmt!</t>
-  </si>
-  <si>
-    <t>Können Sie folgende Zahlen in Binär ausgeben, sodass immer 8 Ziffern geschrieben werden?</t>
+    <t>IP-Adresse</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Meine IP</t>
+  </si>
+  <si>
+    <t>Subnet-Maske</t>
+  </si>
+  <si>
+    <t>Glückwunsch: Sie sind ein Netzwerk-Router</t>
+  </si>
+  <si>
+    <t>Sie sind ein Router und an Ihnen sind verschiedene Netzwerke angeschlossen.</t>
+  </si>
+  <si>
+    <t>IP-Adresse der Schnittstelle</t>
+  </si>
+  <si>
+    <t>Subnet Maske der Schnittstelle</t>
+  </si>
+  <si>
+    <t>Netzwerkadresse an der Schnittstelle</t>
+  </si>
+  <si>
+    <t>IP-Paket hierhin?</t>
+  </si>
+  <si>
+    <t>Summe</t>
+  </si>
+  <si>
+    <t>Schnittstelle 1</t>
+  </si>
+  <si>
+    <t>Schnittstelle 2</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>Leiten Sie IP-Pakete zum Internet-Service-Provider (Swisscom, Sunrise), wenn Sie nicht zu den anderen Netzwerken gehören.</t>
+  </si>
+  <si>
+    <t>Jetzt erhalten Sie ein IP-Paket - wohin damit?</t>
+  </si>
+  <si>
+    <t>Subnet Maske der Schnittstelle (Kopie)</t>
+  </si>
+  <si>
+    <t>Errechnete Netzwerkadresse</t>
   </si>
   <si>
     <t>Ziel-IP-Adresse im Paket</t>
   </si>
   <si>
-    <t>Glückwunsch: Sie sind ein Netzwerk-Router</t>
-  </si>
-  <si>
-    <t>Sie sind ein Router und an Ihnen sind verschiedene Netzwerke angeschlossen.</t>
-  </si>
-  <si>
-    <t>Schnittstelle 1</t>
-  </si>
-  <si>
-    <t>IP-Adresse der Schnittstelle</t>
-  </si>
-  <si>
-    <t>Subnet Maske der Schnittstelle</t>
-  </si>
-  <si>
-    <t>IP-Paket hierhin?</t>
-  </si>
-  <si>
-    <t>Schnittstelle 2</t>
-  </si>
-  <si>
-    <t>Internet</t>
-  </si>
-  <si>
-    <t>Leiten Sie IP-Pakete zum Internet-Service-Provider (Swisscom, Sunrise), wenn Sie nicht zu den anderen Netzwerken gehören.</t>
-  </si>
-  <si>
-    <t>Jetzt erhalten Sie ein IP-Paket - wohin damit?</t>
-  </si>
-  <si>
-    <t>Netzwerkadresse an der Schnittstelle</t>
-  </si>
-  <si>
-    <t>Errechnete Netzwerkadresse</t>
-  </si>
-  <si>
-    <t>1. Byte gleich?</t>
-  </si>
-  <si>
-    <t>2. Byte gleich?</t>
-  </si>
-  <si>
-    <t>3. Byte gleich?</t>
-  </si>
-  <si>
-    <t>4. Byte gleich?</t>
-  </si>
-  <si>
-    <t>Subnet Maske der Schnittstelle (Kopie)</t>
-  </si>
-  <si>
-    <t>Summe</t>
+    <t>👆 daraus kann man herleiten:</t>
+  </si>
+  <si>
+    <t>Netzwerk-Adresse (tiefste Adresse)</t>
+  </si>
+  <si>
+    <t>Letzte IP für Gerät</t>
+  </si>
+  <si>
+    <t>…alle weiteren IPs die Geräte…</t>
+  </si>
+  <si>
+    <t>1. IP für Gerät (oft der Gateway)</t>
+  </si>
+  <si>
+    <t>Broadcast-Adresse (höchste Adresse)</t>
+  </si>
+  <si>
+    <t>2. IP für Gerät (oft der Gateway)</t>
+  </si>
+  <si>
+    <t>Byte</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>👆</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> daraus ergibt sich folgende Netzwerkadresse:</t>
+    </r>
+  </si>
+  <si>
+    <t>Bit-AND</t>
+  </si>
+  <si>
+    <t>Zieladresse des erhaltene Pakets</t>
+  </si>
+  <si>
+    <t>Byte-weise Vergleich mit Original</t>
+  </si>
+  <si>
+    <t>Summe=4 ?</t>
+  </si>
+  <si>
+    <t>Anzahl "4" bei Summe</t>
+  </si>
+  <si>
+    <t>Anzahl = 0?</t>
+  </si>
+  <si>
+    <r>
+      <t>Grundidee: Wir schauen, ob durch ein Bitwise AND (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) mit der gleichen Subnetmaske nochmal die gleiche Netzwerkadresse entsteht. Falls ja, ist es das gleiche Netzwerk!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Die Subnetmaske zieht also </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>eine</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> klare Grenze.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sie muss deswegen aus einer Serie '1' sein und dann nur noch '0'.</t>
+  </si>
+  <si>
+    <t>Subnetmasken mit mehr als einer Grenze zwischen '1' zu '0' sind ungültig!</t>
+  </si>
+  <si>
+    <t>👆 daraus kann man das gesamte Netzwerk herleiten:</t>
+  </si>
+  <si>
+    <t>Die einzigen möglichen Dezimalzahlen sind:</t>
+  </si>
+  <si>
+    <t>Welche IP-Adressen gehören also zum gleichen Netzwerk?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,8 +604,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -551,8 +704,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFAFAF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -692,11 +851,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF00B050"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF00B050"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF00B050"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -724,37 +969,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -764,16 +1054,55 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9797"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9797"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9797"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9797"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9797"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -844,40 +1173,12 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFAFAF"/>
+      <color rgb="FFFF9797"/>
       <color rgb="FFFF0000"/>
     </mruColors>
   </colors>
@@ -1107,23 +1408,26 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>545171</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>120001</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>99837</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>178739</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>725000</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>39175</xdr:rowOff>
+      <xdr:colOff>602075</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1">
+        <xdr:cNvPr id="2" name="Oval 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29A35466-7298-4D64-A1C3-E7993A30D238}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{970B6FB0-D040-464E-9A2F-04C5A9D04145}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{29A35466-7298-4D64-A1C3-E7993A30D238}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1131,27 +1435,23 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4545171" y="685001"/>
-          <a:ext cx="2449829" cy="1629174"/>
+          <a:off x="7510287" y="5595289"/>
+          <a:ext cx="603838" cy="202261"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="ellipse">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000">
-            <a:alpha val="9020"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln>
+        <a:noFill/>
+        <a:ln w="38100">
           <a:solidFill>
-            <a:srgbClr val="C00000"/>
+            <a:srgbClr val="FF0000"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
           <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
+            <a:shade val="15000"/>
           </a:schemeClr>
         </a:lnRef>
         <a:fillRef idx="1">
@@ -1169,7 +1469,987 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="de-CH" sz="1100"/>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>587964</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>183444</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>65855</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>70791</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Oval 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BA8599E-6B12-42C1-9867-AD37A40BC1B1}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3E62796F-241B-F541-067D-137D3746E82A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5814014" y="5218994"/>
+          <a:ext cx="824091" cy="268347"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>530413</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>173868</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>698510</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>75595</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4" name="Gruppieren 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C33A6782-593B-4D52-A789-734E41623799}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="5754044" y="362856"/>
+          <a:ext cx="2443514" cy="5465537"/>
+          <a:chOff x="5754044" y="362856"/>
+          <a:chExt cx="2443514" cy="5397501"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="Rectangle 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65ADFB05-7743-CB23-5939-419A158F99DE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5835952" y="362856"/>
+            <a:ext cx="2281128" cy="5397501"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000">
+              <a:alpha val="9020"/>
+            </a:srgbClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="de-CH" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="Textfeld 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC40EF5B-AC35-5141-4B41-0FAB269E2496}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5754044" y="778631"/>
+            <a:ext cx="2443514" cy="596047"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="2000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Netzwerkteil</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>(definiert durch Subnetmaske)</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>18814</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>28222</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>296331</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>11524</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Oval 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5D475C1-E94C-45D0-A284-CFF0D4D49040}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3E62796F-241B-F541-067D-137D3746E82A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3016014" y="5254272"/>
+          <a:ext cx="277517" cy="173802"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>111949</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23518</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>4704</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>183445</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Oval 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA785020-C5F5-4193-B66B-389FD6698E9E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3E62796F-241B-F541-067D-137D3746E82A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3864799" y="5630568"/>
+          <a:ext cx="337255" cy="159927"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>323894</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>23359</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>663302</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>183286</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Oval 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AC1E292-603D-4A84-9B76-314403861DA8}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3E62796F-241B-F541-067D-137D3746E82A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7835944" y="4868409"/>
+          <a:ext cx="339408" cy="159927"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>97877</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>17979</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>308132</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>177906</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Oval 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49F1E781-4B17-4BA6-8E72-7F1838F211DA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3E62796F-241B-F541-067D-137D3746E82A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3850727" y="4863029"/>
+          <a:ext cx="337255" cy="159927"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1182,16 +2462,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>41412</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>165651</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>578138</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>150531</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>175351</xdr:rowOff>
+      <xdr:colOff>400655</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>160230</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1221,8 +2501,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3975651" y="2767771"/>
-          <a:ext cx="4693479" cy="1127852"/>
+          <a:off x="3911888" y="4225114"/>
+          <a:ext cx="4736207" cy="1098271"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1244,15 +2524,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>351368</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>155721</xdr:rowOff>
+      <xdr:colOff>275773</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>140600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>12050</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>155721</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>548776</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>102803</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1267,8 +2547,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="6924680" y="4049499"/>
-          <a:ext cx="1093033" cy="269657"/>
+          <a:off x="6890787" y="5530110"/>
+          <a:ext cx="1088572" cy="273003"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1321,16 +2601,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>18467</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>154008</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>41146</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>138887</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>288124</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>154009</xdr:rowOff>
+      <xdr:colOff>212529</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>101091</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1345,8 +2625,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="6591779" y="4047786"/>
-          <a:ext cx="1093034" cy="269657"/>
+          <a:off x="6556212" y="5530071"/>
+          <a:ext cx="1088573" cy="269657"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1400,15 +2680,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>411188</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>140535</xdr:rowOff>
+      <xdr:colOff>335593</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>125414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>71869</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>140536</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>608596</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>87618</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1423,8 +2703,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="5579172" y="4034313"/>
-          <a:ext cx="1093034" cy="269657"/>
+          <a:off x="5529415" y="5514925"/>
+          <a:ext cx="1088573" cy="273003"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1470,13 +2750,878 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>529167</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>103949</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>230498</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Freihandform: Form 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A39615DE-71F2-4CA3-5CCD-42CAE047E225}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8770608" y="3654074"/>
+          <a:ext cx="2752043" cy="440981"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 104337"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 104337"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 379633"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 379633"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 535394"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 535394"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 491891"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 491891"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 388880"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 388880"/>
+            <a:gd name="connsiteX0" fmla="*/ 2713869 w 2713869"/>
+            <a:gd name="connsiteY0" fmla="*/ 0 h 435869"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2713869"/>
+            <a:gd name="connsiteY1" fmla="*/ 90714 h 435869"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX0" y="connsiteY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX1" y="connsiteY1"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="2713869" h="435869">
+              <a:moveTo>
+                <a:pt x="2713869" y="0"/>
+              </a:moveTo>
+              <a:cubicBezTo>
+                <a:pt x="2436055" y="478140"/>
+                <a:pt x="653899" y="638780"/>
+                <a:pt x="0" y="90714"/>
+              </a:cubicBezTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>468686</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>165581</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>366311</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>25381</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Freihandform: Form 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{264C19DB-07DB-4487-BA77-620F2397E1EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="643691">
+          <a:off x="8710127" y="2185830"/>
+          <a:ext cx="2948337" cy="1206633"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 104337"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 104337"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 379633"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 379633"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 535394"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 535394"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 491891"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 491891"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 388880"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 388880"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1253165"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1253165"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1267068"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1267068"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1132694"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1132694"/>
+            <a:gd name="connsiteX0" fmla="*/ 2993942 w 2993942"/>
+            <a:gd name="connsiteY0" fmla="*/ 1011274 h 1011274"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2993942"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1011274"/>
+            <a:gd name="connsiteX0" fmla="*/ 2921308 w 2921308"/>
+            <a:gd name="connsiteY0" fmla="*/ 1155833 h 1155833"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2921308"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1155833"/>
+            <a:gd name="connsiteX0" fmla="*/ 2921308 w 2921308"/>
+            <a:gd name="connsiteY0" fmla="*/ 1159722 h 1159722"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2921308"/>
+            <a:gd name="connsiteY1" fmla="*/ 3889 h 1159722"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX0" y="connsiteY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX1" y="connsiteY1"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="2921308" h="1159722">
+              <a:moveTo>
+                <a:pt x="2921308" y="1159722"/>
+              </a:moveTo>
+              <a:cubicBezTo>
+                <a:pt x="1309711" y="120941"/>
+                <a:pt x="305446" y="-28323"/>
+                <a:pt x="0" y="3889"/>
+              </a:cubicBezTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>570727</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>87105</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>538079</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>135215</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Freihandform: Form 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C62BF4B-B8E7-4C30-BE3B-F3FCD3737D81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="643691">
+          <a:off x="11846601" y="2115406"/>
+          <a:ext cx="3130022" cy="794081"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 104337"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 104337"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 379633"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 379633"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 535394"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 535394"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 491891"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 491891"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 388880"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 388880"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1253165"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1253165"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1267068"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1267068"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1132694"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1132694"/>
+            <a:gd name="connsiteX0" fmla="*/ 2993942 w 2993942"/>
+            <a:gd name="connsiteY0" fmla="*/ 1011274 h 1011274"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2993942"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1011274"/>
+            <a:gd name="connsiteX0" fmla="*/ 2921308 w 2921308"/>
+            <a:gd name="connsiteY0" fmla="*/ 1155833 h 1155833"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2921308"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1155833"/>
+            <a:gd name="connsiteX0" fmla="*/ 2921308 w 2921308"/>
+            <a:gd name="connsiteY0" fmla="*/ 1159722 h 1159722"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2921308"/>
+            <a:gd name="connsiteY1" fmla="*/ 3889 h 1159722"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX0" y="connsiteY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX1" y="connsiteY1"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="2921308" h="1159722">
+              <a:moveTo>
+                <a:pt x="2921308" y="1159722"/>
+              </a:moveTo>
+              <a:cubicBezTo>
+                <a:pt x="1309711" y="120941"/>
+                <a:pt x="305446" y="-28323"/>
+                <a:pt x="0" y="3889"/>
+              </a:cubicBezTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="00B0F0"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>608103</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>121807</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>707971</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>112920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Freihandform: Form 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FA502FB-B5D6-43B3-8B1C-4405685D6845}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="643691" flipV="1">
+          <a:off x="11883977" y="2520011"/>
+          <a:ext cx="5771712" cy="182229"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 104337"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 104337"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 379633"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 379633"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 535394"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 535394"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 491891"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 491891"/>
+            <a:gd name="connsiteX0" fmla="*/ 2849941 w 2849941"/>
+            <a:gd name="connsiteY0" fmla="*/ 7559 h 388880"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2849941"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 388880"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1253165"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1253165"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1267068"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1267068"/>
+            <a:gd name="connsiteX0" fmla="*/ 3124662 w 3124662"/>
+            <a:gd name="connsiteY0" fmla="*/ 1132694 h 1132694"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 3124662"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1132694"/>
+            <a:gd name="connsiteX0" fmla="*/ 2993942 w 2993942"/>
+            <a:gd name="connsiteY0" fmla="*/ 1011274 h 1011274"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2993942"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1011274"/>
+            <a:gd name="connsiteX0" fmla="*/ 2921308 w 2921308"/>
+            <a:gd name="connsiteY0" fmla="*/ 1155833 h 1155833"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2921308"/>
+            <a:gd name="connsiteY1" fmla="*/ 0 h 1155833"/>
+            <a:gd name="connsiteX0" fmla="*/ 2921308 w 2921308"/>
+            <a:gd name="connsiteY0" fmla="*/ 1159722 h 1159722"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2921308"/>
+            <a:gd name="connsiteY1" fmla="*/ 3889 h 1159722"/>
+            <a:gd name="connsiteX0" fmla="*/ 2921308 w 2921308"/>
+            <a:gd name="connsiteY0" fmla="*/ 1155841 h 1639221"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2921308"/>
+            <a:gd name="connsiteY1" fmla="*/ 8 h 1639221"/>
+            <a:gd name="connsiteX0" fmla="*/ 2921308 w 2921308"/>
+            <a:gd name="connsiteY0" fmla="*/ 1155841 h 4622475"/>
+            <a:gd name="connsiteX1" fmla="*/ 0 w 2921308"/>
+            <a:gd name="connsiteY1" fmla="*/ 8 h 4622475"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX0" y="connsiteY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX1" y="connsiteY1"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="2921308" h="4622475">
+              <a:moveTo>
+                <a:pt x="2921308" y="1155841"/>
+              </a:moveTo>
+              <a:cubicBezTo>
+                <a:pt x="2316149" y="7763463"/>
+                <a:pt x="561977" y="3517772"/>
+                <a:pt x="0" y="8"/>
+              </a:cubicBezTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>496957</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>49697</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>71785</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>77305</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Textfeld 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B3582EC-75E8-9674-6B69-FD5DEF37828C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4527827" y="3290958"/>
+          <a:ext cx="425175" cy="585304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="de-DE" sz="3200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>&amp;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>507999</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>93869</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>82827</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>99390</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Textfeld 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24DD8DAA-CEC9-490B-A4D7-03D31975E68F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4538869" y="1568173"/>
+          <a:ext cx="425175" cy="585304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="de-DE" sz="3200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>&amp;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>132521</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>71783</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>557696</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>77304</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Textfeld 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D4D03A8-B0DC-4EEC-8379-E09B1F20674A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7741478" y="1546087"/>
+          <a:ext cx="425175" cy="585304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="de-DE" sz="3200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>=</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>108225</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>180008</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Textfeld 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{910D91AE-70CD-448D-A057-C64D80220408}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7717182" y="3393661"/>
+          <a:ext cx="425175" cy="585304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="de-DE" sz="3200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>=</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>36548</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>169029</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>86800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rechteck 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E61ECDA5-C475-BC1A-269D-056D70541714}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2946584"/>
+          <a:ext cx="9292015" cy="5660180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1514,7 +3659,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1620,7 +3765,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1762,7 +3907,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1880,12 +4025,12 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -1941,37 +4086,37 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
@@ -2012,7 +4157,7 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
@@ -2033,7 +4178,7 @@
     </row>
     <row r="46" spans="1:22" ht="28.5" x14ac:dyDescent="0.65">
       <c r="A46" s="8" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -2059,20 +4204,20 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
@@ -2080,7 +4225,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -2119,7 +4264,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -2158,7 +4303,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -2172,12 +4317,12 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B64" s="6"/>
     </row>
@@ -2237,7 +4382,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B67" s="6">
         <v>7</v>
@@ -2251,12 +4396,12 @@
       <c r="J67" s="5"/>
       <c r="K67" s="3"/>
       <c r="L67" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
@@ -2270,12 +4415,12 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
@@ -2397,7 +4542,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C88" s="5"/>
     </row>
@@ -2409,23 +4554,23 @@
         <v>35</v>
       </c>
       <c r="E89" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C94" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E94" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
@@ -2433,7 +4578,7 @@
         <v>5</v>
       </c>
       <c r="C95" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E95">
         <v>5</v>
@@ -2497,12 +4642,12 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
@@ -2547,7 +4692,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.35">
@@ -2555,12 +4700,12 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.35">
@@ -2697,17 +4842,17 @@
     </row>
     <row r="137" spans="1:10" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.7">
       <c r="A137" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.35">
@@ -2760,27 +4905,27 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2815,12 +4960,12 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2909,27 +5054,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A119">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>255</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C61">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>5342</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>82</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>169</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2940,661 +5085,1308 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC0886E-6230-44AA-AB02-85890F3B0BBF}">
-  <dimension ref="A2:T16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A872A64-36A2-4EDA-B35E-1B56D6FE03BB}">
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="1.7265625" customWidth="1"/>
-    <col min="4" max="4" width="5.08984375" customWidth="1"/>
-    <col min="5" max="5" width="1.81640625" customWidth="1"/>
-    <col min="6" max="6" width="5.54296875" customWidth="1"/>
-    <col min="7" max="7" width="1.453125" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.453125" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="1.453125" customWidth="1"/>
-    <col min="15" max="15" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="1.453125" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.90625" customWidth="1"/>
+    <col min="2" max="2" width="4.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.7265625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="4.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.81640625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="4.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.453125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="4.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.453125" style="20" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="1.453125" style="20" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="1.453125" style="20" customWidth="1"/>
+    <col min="17" max="17" width="10.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7.1796875" customWidth="1"/>
-    <col min="21" max="21" width="10.6328125" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" customWidth="1"/>
     <col min="22" max="22" width="10.26953125" customWidth="1"/>
+    <col min="23" max="23" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.4">
-      <c r="S2" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
-      <c r="S3" s="16">
+    <row r="1" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="T1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="11"/>
+    </row>
+    <row r="2" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="43">
+        <v>1</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43">
+        <v>2</v>
+      </c>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43">
+        <v>3</v>
+      </c>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43">
+        <v>4</v>
+      </c>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="43">
+        <v>1</v>
+      </c>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43">
+        <v>2</v>
+      </c>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43">
+        <v>3</v>
+      </c>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A3" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="44">
+        <v>192</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="44">
+        <v>168</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="44">
+        <v>6</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="44">
+        <v>6</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="44" t="str">
+        <f>DEC2BIN(B3,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3" s="44" t="str">
+        <f>DEC2BIN(D3,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3" s="44" t="str">
+        <f>DEC2BIN(F3,8)</f>
+        <v>00000110</v>
+      </c>
+      <c r="P3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="44" t="str">
+        <f>DEC2BIN(H3,8)</f>
+        <v>00000110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="44">
         <v>255</v>
       </c>
-      <c r="T3" s="11" t="str">
-        <f>DEC2BIN(S3,8)</f>
+      <c r="C4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="44">
+        <v>255</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="44">
+        <v>254</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="44">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="44" t="str">
+        <f>DEC2BIN(B4,8)</f>
         <v>11111111</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
-      <c r="S4" s="11">
+      <c r="L4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4" s="44" t="str">
+        <f>DEC2BIN(D4,8)</f>
+        <v>11111111</v>
+      </c>
+      <c r="N4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="44" t="str">
+        <f>DEC2BIN(F4,8)</f>
+        <v>11111110</v>
+      </c>
+      <c r="P4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="44" t="str">
+        <f>DEC2BIN(H4,8)</f>
+        <v>00000000</v>
+      </c>
+      <c r="W4" s="11"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A5" s="11"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="S5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="V5" s="11"/>
+    </row>
+    <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="S6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="V6" s="11"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="S7" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="V8" s="11"/>
+    </row>
+    <row r="9" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="47">
+        <f>_xlfn.BITAND($B$3,$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="47">
+        <f>_xlfn.BITAND($D$3,$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="47">
+        <f>_xlfn.BITAND($F$3,$F$4)</f>
+        <v>6</v>
+      </c>
+      <c r="G9" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="47">
+        <f>_xlfn.BITAND($H$3,$H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="47" t="str">
+        <f>DEC2BIN(B9,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L9" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="47" t="str">
+        <f t="shared" ref="M9:Q9" si="0">DEC2BIN(D9,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N9" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>00000110</v>
+      </c>
+      <c r="P9" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>00000000</v>
+      </c>
+      <c r="V9" s="11"/>
+    </row>
+    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="46">
+        <f>_xlfn.BITAND($B$3,$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="46">
+        <f>_xlfn.BITAND($D$3,$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="46">
+        <f>_xlfn.BITAND($F$3,$F$4)</f>
+        <v>6</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="46">
+        <f>_xlfn.BITAND($H$3,$H$4)+1</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="42"/>
+      <c r="J10" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="46" t="str">
+        <f>DEC2BIN(B10,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L10" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="46" t="str">
+        <f>DEC2BIN(D10,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N10" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="46" t="str">
+        <f>DEC2BIN(F10,8)</f>
+        <v>00000110</v>
+      </c>
+      <c r="P10" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q10" s="46" t="str">
+        <f>DEC2BIN(H10,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="S10" s="11"/>
+      <c r="T10" s="16">
+        <v>255</v>
+      </c>
+      <c r="U10" s="11" t="str">
+        <f>DEC2BIN(T10,8)</f>
+        <v>11111111</v>
+      </c>
+      <c r="V10" s="11"/>
+    </row>
+    <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="46">
+        <f>_xlfn.BITAND($B$3,$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="46">
+        <f>_xlfn.BITAND($D$3,$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="46">
+        <f>_xlfn.BITAND($F$3,$F$4)</f>
+        <v>6</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="46">
+        <f>_xlfn.BITAND($H$3,$H$4)+2</f>
+        <v>2</v>
+      </c>
+      <c r="I11" s="42"/>
+      <c r="J11" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="46" t="str">
+        <f>DEC2BIN(B11,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L11" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="46" t="str">
+        <f>DEC2BIN(D11,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N11" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O11" s="46" t="str">
+        <f>DEC2BIN(F11,8)</f>
+        <v>00000110</v>
+      </c>
+      <c r="P11" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q11" s="46" t="str">
+        <f>DEC2BIN(H11,8)</f>
+        <v>00000010</v>
+      </c>
+      <c r="T11" s="11">
         <v>254</v>
       </c>
-      <c r="T4" s="11" t="str">
-        <f t="shared" ref="T4:T11" si="0">DEC2BIN(S4,8)</f>
+      <c r="U11" s="11" t="str">
+        <f>DEC2BIN(T11,8)</f>
         <v>11111110</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
-      <c r="A5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="V11" s="11"/>
+    </row>
+    <row r="12" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A12" s="42"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="16">
+        <v>252</v>
+      </c>
+      <c r="U12" s="11" t="str">
+        <f>DEC2BIN(T12,8)</f>
+        <v>11111100</v>
+      </c>
+      <c r="V12" s="11"/>
+    </row>
+    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A13" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="T13" s="11">
+        <v>248</v>
+      </c>
+      <c r="U13" s="11" t="str">
+        <f>DEC2BIN(T13,8)</f>
+        <v>11111000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A14" s="42"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="T14" s="11">
+        <v>240</v>
+      </c>
+      <c r="U14" s="11" t="str">
+        <f>DEC2BIN(T14,8)</f>
+        <v>11110000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="46">
+        <f>_xlfn.BITAND($B$3,$B$4)+(255-$B$4)</f>
         <v>192</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="C15" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="46">
+        <f>_xlfn.BITAND($D$3,$D$4)+(255-$D$4)</f>
         <v>168</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="12">
-        <v>2</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="12">
+      <c r="E15" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="46">
+        <f>_xlfn.BITAND($F$3,$F$4)+(255-$F$4)</f>
+        <v>7</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="46">
+        <f>_xlfn.BITAND($H$3,$H$4)+(255-$H$4)-2</f>
+        <v>253</v>
+      </c>
+      <c r="I15" s="42"/>
+      <c r="J15" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="46" t="str">
+        <f>DEC2BIN(B15,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="46" t="str">
+        <f>DEC2BIN(D15,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N15" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O15" s="46" t="str">
+        <f>DEC2BIN(F15,8)</f>
+        <v>00000111</v>
+      </c>
+      <c r="P15" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q15" s="46" t="str">
+        <f>DEC2BIN(H15,8)</f>
+        <v>11111101</v>
+      </c>
+      <c r="T15" s="11">
+        <v>224</v>
+      </c>
+      <c r="U15" s="11" t="str">
+        <f>DEC2BIN(T15,8)</f>
+        <v>11100000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A16" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="46">
+        <f>_xlfn.BITAND($B$3,$B$4)+(255-$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="46">
+        <f>_xlfn.BITAND($D$3,$D$4)+(255-$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="46">
+        <f>_xlfn.BITAND($F$3,$F$4)+(255-$F$4)</f>
+        <v>7</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="46">
+        <f>_xlfn.BITAND($H$3,$H$4)+(255-$H$4)-1</f>
+        <v>254</v>
+      </c>
+      <c r="I16" s="42"/>
+      <c r="J16" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="46" t="str">
+        <f>DEC2BIN(B16,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="46" t="str">
+        <f>DEC2BIN(D16,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O16" s="46" t="str">
+        <f>DEC2BIN(F16,8)</f>
+        <v>00000111</v>
+      </c>
+      <c r="P16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q16" s="46" t="str">
+        <f>DEC2BIN(H16,8)</f>
+        <v>11111110</v>
+      </c>
+      <c r="T16" s="11">
+        <v>192</v>
+      </c>
+      <c r="U16" s="11" t="str">
+        <f>DEC2BIN(T16,8)</f>
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="47">
+        <f>_xlfn.BITAND($B$3,$B$4)+(255-$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="47">
+        <f>_xlfn.BITAND($D$3,$D$4)+(255-$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="47">
+        <f>_xlfn.BITAND($F$3,$F$4)+(255-$F$4)</f>
+        <v>7</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="47">
+        <f>_xlfn.BITAND($H$3,$H$4)+(255-$H$4)</f>
+        <v>255</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="47" t="str">
+        <f>DEC2BIN(B17,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L17" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="47" t="str">
+        <f>DEC2BIN(D17,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N17" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="O17" s="47" t="str">
+        <f>DEC2BIN(F17,8)</f>
+        <v>00000111</v>
+      </c>
+      <c r="P17" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q17" s="47" t="str">
+        <f>DEC2BIN(H17,8)</f>
+        <v>11111111</v>
+      </c>
+      <c r="T17" s="11">
+        <v>128</v>
+      </c>
+      <c r="U17" s="11" t="str">
+        <f>DEC2BIN(T17,8)</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="T18" s="11">
+        <v>0</v>
+      </c>
+      <c r="U18" s="11" t="str">
+        <f>DEC2BIN(T18,8)</f>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+    </row>
+    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="46">
+        <v>192</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="46">
+        <v>168</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="46">
+        <v>6</v>
+      </c>
+      <c r="G21" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" s="46">
         <v>13</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="12" t="str">
-        <f t="shared" ref="K5:K10" si="1">DEC2BIN(B5,8)</f>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" s="46" t="str">
+        <f t="shared" ref="K21:K30" si="1">DEC2BIN(B21,8)</f>
         <v>11000000</v>
       </c>
-      <c r="L5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="12" t="str">
-        <f t="shared" ref="M5:M10" si="2">DEC2BIN(D5,8)</f>
+      <c r="L21" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="46" t="str">
+        <f t="shared" ref="M21:M30" si="2">DEC2BIN(D21,8)</f>
         <v>10101000</v>
       </c>
-      <c r="N5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="12" t="str">
-        <f t="shared" ref="O5:O10" si="3">DEC2BIN(F5,8)</f>
-        <v>00000010</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="12" t="str">
-        <f t="shared" ref="Q5:Q10" si="4">DEC2BIN(H5,8)</f>
+      <c r="N21" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O21" s="46" t="str">
+        <f t="shared" ref="O21:O30" si="3">DEC2BIN(F21,8)</f>
+        <v>00000110</v>
+      </c>
+      <c r="P21" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q21" s="46" t="str">
+        <f t="shared" ref="Q21:Q30" si="4">DEC2BIN(H21,8)</f>
         <v>00001101</v>
       </c>
-      <c r="S5" s="16">
-        <v>252</v>
-      </c>
-      <c r="T5" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>11111100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
-      <c r="A6" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="12">
+    </row>
+    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A22" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="50">
+        <f>_xlfn.BITAND(B21,B$4)</f>
         <v>192</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C22" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="50">
+        <f>_xlfn.BITAND(D21,D$4)</f>
         <v>168</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="12">
-        <v>2</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="12">
-        <v>41</v>
-      </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="12" t="str">
+      <c r="E22" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="50">
+        <f>_xlfn.BITAND(F21,F$4)</f>
+        <v>6</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="50">
+        <f>_xlfn.BITAND(H21,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="43" t="str">
         <f t="shared" si="1"/>
         <v>11000000</v>
       </c>
-      <c r="L6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="12" t="str">
+      <c r="L22" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="43" t="str">
         <f t="shared" si="2"/>
         <v>10101000</v>
       </c>
-      <c r="N6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" s="12" t="str">
+      <c r="N22" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O22" s="43" t="str">
         <f t="shared" si="3"/>
-        <v>00000010</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" s="12" t="str">
+        <v>00000110</v>
+      </c>
+      <c r="P22" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q22" s="43" t="str">
+        <f t="shared" si="4"/>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A23" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="46">
+        <v>192</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="46">
+        <v>168</v>
+      </c>
+      <c r="E23" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="46">
+        <v>7</v>
+      </c>
+      <c r="G23" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" s="46">
+        <v>41</v>
+      </c>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23" s="46" t="str">
+        <f t="shared" si="1"/>
+        <v>11000000</v>
+      </c>
+      <c r="L23" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="46" t="str">
+        <f t="shared" si="2"/>
+        <v>10101000</v>
+      </c>
+      <c r="N23" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O23" s="46" t="str">
+        <f t="shared" si="3"/>
+        <v>00000111</v>
+      </c>
+      <c r="P23" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q23" s="46" t="str">
         <f t="shared" si="4"/>
         <v>00101001</v>
       </c>
-      <c r="S6" s="11">
-        <v>248</v>
-      </c>
-      <c r="T6" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>11111000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
-      <c r="A7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="12">
+    </row>
+    <row r="24" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A24" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="50">
+        <f>_xlfn.BITAND(B23,B$4)</f>
         <v>192</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="C24" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="50">
+        <f>_xlfn.BITAND(D23,D$4)</f>
         <v>168</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="12">
-        <v>2</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="12">
-        <v>51</v>
-      </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="12" t="str">
+      <c r="E24" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="50">
+        <f>_xlfn.BITAND(F23,F$4)</f>
+        <v>6</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" s="50">
+        <f>_xlfn.BITAND(H23,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24" s="43" t="str">
         <f t="shared" si="1"/>
         <v>11000000</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="12" t="str">
+      <c r="L24" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="43" t="str">
         <f t="shared" si="2"/>
         <v>10101000</v>
       </c>
-      <c r="N7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="12" t="str">
+      <c r="N24" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O24" s="43" t="str">
         <f t="shared" si="3"/>
-        <v>00000010</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="12" t="str">
+        <v>00000110</v>
+      </c>
+      <c r="P24" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q24" s="43" t="str">
+        <f t="shared" si="4"/>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A25" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="45">
+        <v>192</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="45">
+        <v>168</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="45">
+        <v>8</v>
+      </c>
+      <c r="G25" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" s="45">
+        <v>255</v>
+      </c>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="45" t="str">
+        <f>DEC2BIN(B25,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L25" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="45" t="str">
+        <f>DEC2BIN(D25,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N25" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="O25" s="45" t="str">
+        <f>DEC2BIN(F25,8)</f>
+        <v>00001000</v>
+      </c>
+      <c r="P25" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q25" s="45" t="str">
+        <f>DEC2BIN(H25,8)</f>
+        <v>11111111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A26" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="50">
+        <f>_xlfn.BITAND(B25,B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="50">
+        <f>_xlfn.BITAND(D25,D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="50">
+        <f>_xlfn.BITAND(F25,F$4)</f>
+        <v>8</v>
+      </c>
+      <c r="G26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" s="50">
+        <f>_xlfn.BITAND(H25,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="43" t="str">
+        <f>DEC2BIN(B26,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L26" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="43" t="str">
+        <f>DEC2BIN(D26,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N26" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O26" s="43" t="str">
+        <f>DEC2BIN(F26,8)</f>
+        <v>00001000</v>
+      </c>
+      <c r="P26" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q26" s="43" t="str">
+        <f>DEC2BIN(H26,8)</f>
+        <v>00000000</v>
+      </c>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+    </row>
+    <row r="27" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A27" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="45">
+        <v>10</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="45">
+        <v>168</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="45">
+        <v>1</v>
+      </c>
+      <c r="G27" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" s="45">
+        <v>51</v>
+      </c>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>00001010</v>
+      </c>
+      <c r="L27" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="45" t="str">
+        <f t="shared" si="2"/>
+        <v>10101000</v>
+      </c>
+      <c r="N27" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="O27" s="45" t="str">
+        <f t="shared" si="3"/>
+        <v>00000001</v>
+      </c>
+      <c r="P27" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q27" s="45" t="str">
         <f t="shared" si="4"/>
         <v>00110011</v>
       </c>
-      <c r="S7" s="11">
-        <v>240</v>
-      </c>
-      <c r="T7" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>11110000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
-      <c r="A8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="12">
+    </row>
+    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A28" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="50">
+        <f>_xlfn.BITAND(B27,B$4)</f>
+        <v>10</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="50">
+        <f>_xlfn.BITAND(D27,D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="50">
+        <f>_xlfn.BITAND(F27,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" s="50">
+        <f>_xlfn.BITAND(H27,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>00001010</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>10101000</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O28" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>00000000</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q28" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>00000000</v>
+      </c>
+      <c r="V28" s="11"/>
+      <c r="W28" s="11"/>
+    </row>
+    <row r="29" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A29" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="45">
         <v>192</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C29" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="45">
         <v>168</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="12">
-        <v>2</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="12">
+      <c r="E29" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="45">
+        <v>50</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" s="45">
         <v>23</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="12" t="str">
+      <c r="I29" s="40"/>
+      <c r="J29" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="45" t="str">
         <f t="shared" si="1"/>
         <v>11000000</v>
       </c>
-      <c r="L8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="12" t="str">
+      <c r="L29" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="45" t="str">
         <f t="shared" si="2"/>
         <v>10101000</v>
       </c>
-      <c r="N8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O8" s="12" t="str">
+      <c r="N29" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="O29" s="45" t="str">
         <f t="shared" si="3"/>
-        <v>00000010</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q8" s="12" t="str">
+        <v>00110010</v>
+      </c>
+      <c r="P29" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q29" s="45" t="str">
         <f t="shared" si="4"/>
         <v>00010111</v>
       </c>
-      <c r="S8" s="11">
-        <v>224</v>
-      </c>
-      <c r="T8" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>11100000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
-      <c r="A9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="12">
+    </row>
+    <row r="30" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A30" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="50">
+        <f>_xlfn.BITAND(B29,B$4)</f>
         <v>192</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="12">
+      <c r="C30" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="50">
+        <f>_xlfn.BITAND(D29,D$4)</f>
         <v>168</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="12">
-        <v>2</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="12">
-        <v>23</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="12" t="str">
+      <c r="E30" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="50">
+        <f>_xlfn.BITAND(F29,F$4)</f>
+        <v>50</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" s="50">
+        <f>_xlfn.BITAND(H29,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30" s="43" t="str">
         <f t="shared" si="1"/>
         <v>11000000</v>
       </c>
-      <c r="L9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="12" t="str">
+      <c r="L30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="43" t="str">
         <f t="shared" si="2"/>
         <v>10101000</v>
       </c>
-      <c r="N9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="12" t="str">
+      <c r="N30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O30" s="43" t="str">
         <f t="shared" si="3"/>
-        <v>00000010</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="12" t="str">
+        <v>00110010</v>
+      </c>
+      <c r="P30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q30" s="43" t="str">
         <f t="shared" si="4"/>
-        <v>00010111</v>
-      </c>
-      <c r="S9" s="11">
-        <v>192</v>
-      </c>
-      <c r="T9" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>11000000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15" x14ac:dyDescent="0.4">
-      <c r="A10" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="12">
-        <v>192</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="12">
-        <v>168</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="12">
-        <v>2</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="12">
-        <v>233</v>
-      </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>11000000</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>10101000</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v>00000010</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q10" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v>11101001</v>
-      </c>
-      <c r="S10" s="11">
-        <v>128</v>
-      </c>
-      <c r="T10" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="15" x14ac:dyDescent="0.4">
-      <c r="A11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="12">
-        <v>192</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="12">
-        <v>168</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="12">
-        <v>2</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="12">
-        <v>6</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="12" t="str">
-        <f>DEC2BIN(B11,8)</f>
-        <v>11000000</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="12" t="str">
-        <f>DEC2BIN(D11,8)</f>
-        <v>10101000</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" s="12" t="str">
-        <f>DEC2BIN(F11,8)</f>
-        <v>00000010</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q11" s="12" t="str">
-        <f>DEC2BIN(H11,8)</f>
-        <v>00000110</v>
-      </c>
-      <c r="S11" s="11">
-        <v>0</v>
-      </c>
-      <c r="T11" s="11" t="str">
-        <f t="shared" si="0"/>
         <v>00000000</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="15" x14ac:dyDescent="0.4">
-      <c r="A12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="13">
-        <v>255</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="13">
-        <v>255</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="13">
-        <v>255</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="13" t="str">
-        <f>DEC2BIN(B12,8)</f>
-        <v>11111111</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="13" t="str">
-        <f>DEC2BIN(D12,8)</f>
-        <v>11111111</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="O12" s="13" t="str">
-        <f>DEC2BIN(F12,8)</f>
-        <v>11111111</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q12" s="13" t="str">
-        <f>DEC2BIN(H12,8)</f>
-        <v>00000000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="15" x14ac:dyDescent="0.4">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="T13" s="11"/>
-    </row>
-    <row r="14" spans="1:20" ht="15" x14ac:dyDescent="0.4">
-      <c r="A14" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="15">
-        <f>_xlfn.BITAND(B11,B12)</f>
-        <v>192</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="15">
-        <f t="shared" ref="D14:H14" si="5">_xlfn.BITAND(D11,D12)</f>
-        <v>168</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="15">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="15" t="str">
-        <f>DEC2BIN(B14,8)</f>
-        <v>11000000</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" s="15" t="str">
-        <f t="shared" ref="M14:Q14" si="6">DEC2BIN(D14,8)</f>
-        <v>10101000</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O14" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>00000010</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q14" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>00000000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="15" x14ac:dyDescent="0.4">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" x14ac:dyDescent="0.4">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
+      <c r="S30"/>
+      <c r="T30"/>
+      <c r="U30"/>
+    </row>
+    <row r="31" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A31"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="U31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3605,651 +6397,547 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763721F9-D241-4071-831B-604643AF0551}">
-  <dimension ref="A1:AD30"/>
+  <dimension ref="A1:AE30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="0.81640625" customWidth="1"/>
-    <col min="4" max="4" width="8.90625" customWidth="1"/>
-    <col min="5" max="5" width="1.08984375" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" customWidth="1"/>
+    <col min="5" max="5" width="1.1796875" customWidth="1"/>
     <col min="7" max="7" width="1.26953125" customWidth="1"/>
-    <col min="9" max="9" width="3.36328125" customWidth="1"/>
-    <col min="11" max="11" width="1.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="1.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.453125" customWidth="1"/>
+    <col min="11" max="11" width="1.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.453125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.7265625" customWidth="1"/>
-    <col min="26" max="29" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="9.08984375" customWidth="1"/>
+    <col min="27" max="27" width="8.90625" customWidth="1"/>
+    <col min="28" max="28" width="13.26953125" customWidth="1"/>
+    <col min="29" max="29" width="2.54296875" customWidth="1"/>
+    <col min="30" max="30" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="31" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:23" ht="31" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="3" spans="1:30" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
       <c r="I3" s="20"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-    </row>
-    <row r="5" spans="1:30" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:23" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
-      <c r="I5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-    </row>
-    <row r="6" spans="1:30" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="6" spans="1:23" ht="19" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B7" s="44" t="s">
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="44" t="s">
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="S7" s="45"/>
-      <c r="T7" s="45"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A8" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="32">
+    </row>
+    <row r="8" spans="1:23" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="28">
         <v>192</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="33">
-        <v>168</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="33">
+      <c r="C8" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="27">
+        <v>12</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="27">
+        <v>2</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="29">
         <v>1</v>
       </c>
-      <c r="G8" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="34">
-        <v>1</v>
-      </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="32">
+      <c r="I8" s="27"/>
+      <c r="J8" s="28">
         <v>255</v>
       </c>
-      <c r="K8" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="33">
+      <c r="K8" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="27">
         <v>255</v>
       </c>
-      <c r="M8" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="N8" s="33">
+      <c r="M8" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="27">
         <v>255</v>
       </c>
-      <c r="O8" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="P8" s="34">
+      <c r="O8" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="P8" s="29">
         <v>0</v>
       </c>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="32">
+      <c r="Q8" s="27"/>
+      <c r="R8" s="28">
         <f>_xlfn.BITAND(B8,J8)</f>
         <v>192</v>
       </c>
-      <c r="S8" s="33">
+      <c r="S8" s="27">
         <f>_xlfn.BITAND(D8,L8)</f>
-        <v>168</v>
-      </c>
-      <c r="T8" s="33">
+        <v>12</v>
+      </c>
+      <c r="T8" s="27">
         <f>_xlfn.BITAND(F8,N8)</f>
-        <v>1</v>
-      </c>
-      <c r="U8" s="34">
+        <v>2</v>
+      </c>
+      <c r="U8" s="29">
         <f>_xlfn.BITAND(H8,P8)</f>
         <v>0</v>
       </c>
-      <c r="W8" s="42" t="str">
-        <f>IF(AD8=4,"Ja","Nein")</f>
+      <c r="W8" s="55" t="str">
+        <f>AB18</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="31">
+        <v>192</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="30">
+        <v>168</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="30">
+        <v>122</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="32">
+        <v>1</v>
+      </c>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31">
+        <v>255</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="30">
+        <v>255</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="30">
+        <v>0</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="P9" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="31">
+        <f>_xlfn.BITAND(B9,J9)</f>
+        <v>192</v>
+      </c>
+      <c r="S9" s="30">
+        <f>_xlfn.BITAND(D9,L9)</f>
+        <v>168</v>
+      </c>
+      <c r="T9" s="30">
+        <f>_xlfn.BITAND(F9,N9)</f>
+        <v>0</v>
+      </c>
+      <c r="U9" s="32">
+        <f>_xlfn.BITAND(H9,P9)</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="56" t="str">
+        <f>AB19</f>
         <v>Nein</v>
       </c>
-      <c r="Z8">
-        <f>IF(R8=R29,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AA8">
-        <f t="shared" ref="AA8:AC8" si="0">IF(S8=S29,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AB8">
+    </row>
+    <row r="10" spans="1:23" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="68"/>
+      <c r="W10" s="57" t="str">
+        <f>AE20</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="22"/>
+      <c r="H11" s="23"/>
+      <c r="J11" s="22"/>
+      <c r="P11" s="23"/>
+      <c r="R11" s="22"/>
+      <c r="U11" s="23"/>
+      <c r="W11" s="33"/>
+    </row>
+    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="26"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="26"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="26"/>
+      <c r="W12" s="34"/>
+    </row>
+    <row r="14" spans="1:23" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:23" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+    </row>
+    <row r="17" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="62"/>
+      <c r="J17" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="62"/>
+      <c r="R17" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="S17" s="61"/>
+      <c r="T17" s="61"/>
+      <c r="U17" s="62"/>
+      <c r="W17" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="X17" s="61"/>
+      <c r="Y17" s="61"/>
+      <c r="Z17" s="61"/>
+      <c r="AA17" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB17" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD17" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE17" s="54" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18">
+        <v>192</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18">
+        <v>12</v>
+      </c>
+      <c r="J18" s="27">
+        <f t="shared" ref="J18:P19" si="0">J8</f>
+        <v>255</v>
+      </c>
+      <c r="K18" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>.</v>
+      </c>
+      <c r="L18" s="27">
+        <f t="shared" si="0"/>
+        <v>255</v>
+      </c>
+      <c r="M18" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>.</v>
+      </c>
+      <c r="N18" s="27">
+        <f t="shared" si="0"/>
+        <v>255</v>
+      </c>
+      <c r="O18" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>.</v>
+      </c>
+      <c r="P18" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC8">
+      <c r="R18" s="27">
+        <f>_xlfn.BITAND(B18,J18)</f>
+        <v>192</v>
+      </c>
+      <c r="S18" s="27">
+        <f>_xlfn.BITAND(L18,D18)</f>
+        <v>12</v>
+      </c>
+      <c r="T18" s="27">
+        <f>_xlfn.BITAND(N18,F18)</f>
+        <v>2</v>
+      </c>
+      <c r="U18" s="27">
+        <f>_xlfn.BITAND(H18,P18)</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="58">
+        <f>IF(R8=R18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X18" s="58">
+        <f>IF(S8=S18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y18" s="58">
+        <f>IF(T8=T18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z18" s="58">
+        <f>IF(U8=U18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA18" s="58">
+        <f>SUM(W18:Z18)</f>
+        <v>4</v>
+      </c>
+      <c r="AB18" s="58" t="str">
+        <f>IF(AA18=4,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="20"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="J19" s="30">
         <f t="shared" si="0"/>
+        <v>255</v>
+      </c>
+      <c r="K19" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v>.</v>
+      </c>
+      <c r="L19" s="30">
+        <f t="shared" si="0"/>
+        <v>255</v>
+      </c>
+      <c r="M19" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v>.</v>
+      </c>
+      <c r="N19" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v>.</v>
+      </c>
+      <c r="P19" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="30">
+        <f>_xlfn.BITAND(J19,B18)</f>
+        <v>192</v>
+      </c>
+      <c r="S19" s="30">
+        <f>_xlfn.BITAND(D18,L19)</f>
+        <v>12</v>
+      </c>
+      <c r="T19" s="30">
+        <f>_xlfn.BITAND(F18,N19)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="30">
+        <f>_xlfn.BITAND(H18,P19)</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="59">
+        <f>IF(R9=R19,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AD8">
-        <f>SUM(Z8:AC8)</f>
+      <c r="X19" s="59">
+        <f>IF(S9=S19,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="59">
+        <f>IF(T9=T19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z19" s="59">
+        <f>IF(U9=U19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA19" s="59">
+        <f>SUM(W19:Z19)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A9" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="36">
-        <v>192</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="37">
-        <v>168</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="37">
-        <v>2</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="38">
+      <c r="AB19" s="59" t="str">
+        <f>IF(AA19=4,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+      <c r="AD19" s="20"/>
+      <c r="AE19" s="20"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AD20" s="51">
+        <f>COUNTIF(AA18:AA19,"=4")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36">
-        <v>255</v>
-      </c>
-      <c r="K9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="37">
-        <v>255</v>
-      </c>
-      <c r="M9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="N9" s="37">
-        <v>255</v>
-      </c>
-      <c r="O9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="36">
-        <f>_xlfn.BITAND(B9,J9)</f>
-        <v>192</v>
-      </c>
-      <c r="S9" s="37">
-        <f>_xlfn.BITAND(D9,L9)</f>
-        <v>168</v>
-      </c>
-      <c r="T9" s="37">
-        <f>_xlfn.BITAND(F9,N9)</f>
-        <v>2</v>
-      </c>
-      <c r="U9" s="38">
-        <f>_xlfn.BITAND(H9,P9)</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="42" t="str">
-        <f>IF(AD9=4,"Ja","Nein")</f>
-        <v>Ja</v>
-      </c>
-      <c r="Z9">
-        <f>IF(R9=R30,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AA9">
-        <f t="shared" ref="AA9:AC9" si="1">IF(S9=S30,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AB9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AD9">
-        <f>SUM(Z9:AC9)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A10" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="41"/>
-      <c r="W10" s="42" t="str">
-        <f>IF(COUNTIF(AD8:AD9,"=4")=0,"Ja", "Nein")</f>
+      <c r="AE20" s="51" t="str">
+        <f>IF(AD20=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="27"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="27"/>
-      <c r="W11" s="42"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="30"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="30"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="30"/>
-      <c r="W12" s="43"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-    </row>
-    <row r="14" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="21"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-    </row>
-    <row r="15" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="21"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-    </row>
-    <row r="16" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="J18" s="21"/>
-    </row>
-    <row r="25" spans="1:21" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-    </row>
-    <row r="27" spans="1:21" ht="19" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="22" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="J28" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="46"/>
-      <c r="R28" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="46"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A29" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29">
-        <v>192</v>
-      </c>
-      <c r="C29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29">
-        <v>168</v>
-      </c>
-      <c r="E29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29">
-        <v>2</v>
-      </c>
-      <c r="G29" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29">
-        <v>12</v>
-      </c>
-      <c r="J29">
-        <f>J8</f>
-        <v>255</v>
-      </c>
-      <c r="K29" t="str">
-        <f t="shared" ref="K29:P30" si="2">K8</f>
-        <v>.</v>
-      </c>
-      <c r="L29">
-        <f t="shared" si="2"/>
-        <v>255</v>
-      </c>
-      <c r="M29" t="str">
-        <f t="shared" si="2"/>
-        <v>.</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="2"/>
-        <v>255</v>
-      </c>
-      <c r="O29" t="str">
-        <f t="shared" si="2"/>
-        <v>.</v>
-      </c>
-      <c r="P29">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <f>_xlfn.BITAND(B29,J29)</f>
-        <v>192</v>
-      </c>
-      <c r="S29">
-        <f>_xlfn.BITAND(D29,L29)</f>
-        <v>168</v>
-      </c>
-      <c r="T29">
-        <f>_xlfn.BITAND(F29,N29)</f>
-        <v>2</v>
-      </c>
-      <c r="U29">
-        <f>_xlfn.BITAND(H29,P29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A30" s="21"/>
-      <c r="B30">
-        <f>B29</f>
-        <v>192</v>
-      </c>
-      <c r="C30" t="str">
-        <f t="shared" ref="C30:H30" si="3">C29</f>
-        <v>.</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="3"/>
-        <v>168</v>
-      </c>
-      <c r="E30" t="str">
-        <f t="shared" si="3"/>
-        <v>.</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="G30" t="str">
-        <f t="shared" si="3"/>
-        <v>.</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="J30">
-        <f>J9</f>
-        <v>255</v>
-      </c>
-      <c r="K30" t="str">
-        <f t="shared" si="2"/>
-        <v>.</v>
-      </c>
-      <c r="L30">
-        <f t="shared" si="2"/>
-        <v>255</v>
-      </c>
-      <c r="M30" t="str">
-        <f t="shared" si="2"/>
-        <v>.</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="2"/>
-        <v>255</v>
-      </c>
-      <c r="O30" t="str">
-        <f t="shared" si="2"/>
-        <v>.</v>
-      </c>
-      <c r="P30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <f>_xlfn.BITAND(B30,J30)</f>
-        <v>192</v>
-      </c>
-      <c r="S30">
-        <f t="shared" ref="S30" si="4">_xlfn.BITAND(D30,L30)</f>
-        <v>168</v>
-      </c>
-      <c r="T30">
-        <f t="shared" ref="T30" si="5">_xlfn.BITAND(F30,N30)</f>
-        <v>2</v>
-      </c>
-      <c r="U30">
-        <f t="shared" ref="U30" si="6">_xlfn.BITAND(H30,P30)</f>
-        <v>0</v>
-      </c>
-    </row>
+    <row r="21" spans="1:31" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="R28:U28"/>
+  <mergeCells count="8">
+    <mergeCell ref="W17:Z17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="R17:U17"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="J7:P7"/>
     <mergeCell ref="R7:U7"/>
     <mergeCell ref="B10:U10"/>
+    <mergeCell ref="B17:H17"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="W8:W10">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"Nein"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"Ja"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4257,4 +6945,1444 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56DF78BA-236A-4F95-88B7-CB506EE50665}">
+  <dimension ref="A2:W33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="42.90625" customWidth="1"/>
+    <col min="2" max="2" width="4.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.7265625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="4.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.81640625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="4.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.453125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="4.54296875" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.453125" style="20" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="1.453125" style="20" customWidth="1"/>
+    <col min="15" max="15" width="10.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="1.453125" style="20" customWidth="1"/>
+    <col min="17" max="17" width="10.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.1796875" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" customWidth="1"/>
+    <col min="22" max="22" width="10.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="43">
+        <v>1</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43">
+        <v>2</v>
+      </c>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43">
+        <v>3</v>
+      </c>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43">
+        <v>4</v>
+      </c>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="43">
+        <v>1</v>
+      </c>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43">
+        <v>2</v>
+      </c>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43">
+        <v>3</v>
+      </c>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43">
+        <v>4</v>
+      </c>
+      <c r="S2" s="14"/>
+      <c r="T2" s="11"/>
+    </row>
+    <row r="3" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A3" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="44">
+        <v>192</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="44">
+        <v>168</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="44">
+        <v>1</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="44">
+        <v>51</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="44" t="str">
+        <f>DEC2BIN(B3,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3" s="44" t="str">
+        <f>DEC2BIN(D3,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3" s="44" t="str">
+        <f>DEC2BIN(F3,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="P3" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="44" t="str">
+        <f>DEC2BIN(H3,8)</f>
+        <v>00110011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="44">
+        <v>255</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="44">
+        <v>255</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="44">
+        <v>255</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="44">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="44" t="str">
+        <f>DEC2BIN(B4,8)</f>
+        <v>11111111</v>
+      </c>
+      <c r="L4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4" s="44" t="str">
+        <f>DEC2BIN(D4,8)</f>
+        <v>11111111</v>
+      </c>
+      <c r="N4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="44" t="str">
+        <f>DEC2BIN(F4,8)</f>
+        <v>11111111</v>
+      </c>
+      <c r="P4" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="44" t="str">
+        <f>DEC2BIN(H4,8)</f>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A5" s="11"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+    </row>
+    <row r="6" spans="1:23" s="11" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="S6" s="16"/>
+    </row>
+    <row r="7" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="47">
+        <f>_xlfn.BITAND($B$3,$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="47">
+        <f>_xlfn.BITAND($D$3,$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="47">
+        <f>_xlfn.BITAND($F$3,$F$4)</f>
+        <v>1</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="47">
+        <f>_xlfn.BITAND($H$3,$H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="47" t="str">
+        <f>DEC2BIN(B7,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L7" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="47" t="str">
+        <f t="shared" ref="M7:Q7" si="0">DEC2BIN(D7,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N7" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>00000001</v>
+      </c>
+      <c r="P7" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q7" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="46">
+        <f>_xlfn.BITAND($B$3,$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="46">
+        <f>_xlfn.BITAND($D$3,$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="46">
+        <f>_xlfn.BITAND($F$3,$F$4)</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="46">
+        <f>_xlfn.BITAND($H$3,$H$4)+1</f>
+        <v>1</v>
+      </c>
+      <c r="I8" s="42"/>
+      <c r="J8" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="46" t="str">
+        <f>DEC2BIN(B8,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L8" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="46" t="str">
+        <f>DEC2BIN(D8,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N8" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="46" t="str">
+        <f>DEC2BIN(F8,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="P8" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" s="46" t="str">
+        <f>DEC2BIN(H8,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="S8" s="16"/>
+    </row>
+    <row r="9" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="46">
+        <f>_xlfn.BITAND($B$3,$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="46">
+        <f>_xlfn.BITAND($D$3,$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="46">
+        <f>_xlfn.BITAND($F$3,$F$4)</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="46">
+        <f>_xlfn.BITAND($H$3,$H$4)+2</f>
+        <v>2</v>
+      </c>
+      <c r="I9" s="42"/>
+      <c r="J9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="46" t="str">
+        <f>DEC2BIN(B9,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L9" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="46" t="str">
+        <f>DEC2BIN(D9,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N9" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="46" t="str">
+        <f>DEC2BIN(F9,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="P9" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="46" t="str">
+        <f>DEC2BIN(H9,8)</f>
+        <v>00000010</v>
+      </c>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+    </row>
+    <row r="10" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A10" s="42"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+    </row>
+    <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A11" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+    </row>
+    <row r="12" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A12" s="42"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+    </row>
+    <row r="13" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="46">
+        <f>_xlfn.BITAND($B$3,$B$4)+(255-$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="46">
+        <f>_xlfn.BITAND($D$3,$D$4)+(255-$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="46">
+        <f>_xlfn.BITAND($F$3,$F$4)+(255-$F$4)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="46">
+        <f>_xlfn.BITAND($H$3,$H$4)+(255-$H$4)-2</f>
+        <v>253</v>
+      </c>
+      <c r="I13" s="42"/>
+      <c r="J13" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="46" t="str">
+        <f>DEC2BIN(B13,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L13" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="46" t="str">
+        <f>DEC2BIN(D13,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N13" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O13" s="46" t="str">
+        <f>DEC2BIN(F13,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="P13" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q13" s="46" t="str">
+        <f>DEC2BIN(H13,8)</f>
+        <v>11111101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="46">
+        <f>_xlfn.BITAND($B$3,$B$4)+(255-$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="46">
+        <f>_xlfn.BITAND($D$3,$D$4)+(255-$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="46">
+        <f>_xlfn.BITAND($F$3,$F$4)+(255-$F$4)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="46">
+        <f>_xlfn.BITAND($H$3,$H$4)+(255-$H$4)-1</f>
+        <v>254</v>
+      </c>
+      <c r="I14" s="42"/>
+      <c r="J14" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="46" t="str">
+        <f>DEC2BIN(B14,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L14" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="46" t="str">
+        <f>DEC2BIN(D14,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N14" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O14" s="46" t="str">
+        <f>DEC2BIN(F14,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="P14" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q14" s="46" t="str">
+        <f>DEC2BIN(H14,8)</f>
+        <v>11111110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A15" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="47">
+        <f>_xlfn.BITAND($B$3,$B$4)+(255-$B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="47">
+        <f>_xlfn.BITAND($D$3,$D$4)+(255-$D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="47">
+        <f>_xlfn.BITAND($F$3,$F$4)+(255-$F$4)</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="47">
+        <f>_xlfn.BITAND($H$3,$H$4)+(255-$H$4)</f>
+        <v>255</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="47" t="str">
+        <f>DEC2BIN(B15,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L15" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="47" t="str">
+        <f>DEC2BIN(D15,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N15" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="O15" s="47" t="str">
+        <f>DEC2BIN(F15,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="P15" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q15" s="47" t="str">
+        <f>DEC2BIN(H15,8)</f>
+        <v>11111111</v>
+      </c>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+    </row>
+    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A17" s="11"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+    </row>
+    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A18" s="11" t="str">
+        <f>A2</f>
+        <v>Byte</v>
+      </c>
+      <c r="B18" s="43">
+        <f t="shared" ref="B18:Q20" si="1">B2</f>
+        <v>1</v>
+      </c>
+      <c r="C18" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="43">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E18" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="G18" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="43">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="43">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L18" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="43">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="N18" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="P18" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="43">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="str">
+        <f t="shared" ref="A19:P20" si="2">A3</f>
+        <v>Meine IP</v>
+      </c>
+      <c r="B19" s="44">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+      <c r="C19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>.</v>
+      </c>
+      <c r="D19" s="44">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+      <c r="E19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>.</v>
+      </c>
+      <c r="F19" s="44">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>.</v>
+      </c>
+      <c r="H19" s="44">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Binär</v>
+      </c>
+      <c r="K19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>11000000</v>
+      </c>
+      <c r="L19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>.</v>
+      </c>
+      <c r="M19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>10101000</v>
+      </c>
+      <c r="N19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>.</v>
+      </c>
+      <c r="O19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>00000001</v>
+      </c>
+      <c r="P19" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>.</v>
+      </c>
+      <c r="Q19" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>00110011</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A20" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Subnet-Maske</v>
+      </c>
+      <c r="B20" s="44">
+        <f t="shared" si="1"/>
+        <v>255</v>
+      </c>
+      <c r="C20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>.</v>
+      </c>
+      <c r="D20" s="44">
+        <f t="shared" si="1"/>
+        <v>255</v>
+      </c>
+      <c r="E20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>.</v>
+      </c>
+      <c r="F20" s="44">
+        <f t="shared" si="1"/>
+        <v>255</v>
+      </c>
+      <c r="G20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>.</v>
+      </c>
+      <c r="H20" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Binär</v>
+      </c>
+      <c r="K20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>11111111</v>
+      </c>
+      <c r="L20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>.</v>
+      </c>
+      <c r="M20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>11111111</v>
+      </c>
+      <c r="N20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>.</v>
+      </c>
+      <c r="O20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>11111111</v>
+      </c>
+      <c r="P20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>.</v>
+      </c>
+      <c r="Q20" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="43">
+        <v>192</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="43">
+        <v>168</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="43">
+        <v>7</v>
+      </c>
+      <c r="G23" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" s="43">
+        <v>13</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23" s="43" t="str">
+        <f t="shared" ref="K23:K26" si="3">DEC2BIN(B23,8)</f>
+        <v>11000000</v>
+      </c>
+      <c r="L23" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="43" t="str">
+        <f t="shared" ref="M23:M26" si="4">DEC2BIN(D23,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N23" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O23" s="43" t="str">
+        <f t="shared" ref="O23:O26" si="5">DEC2BIN(F23,8)</f>
+        <v>00000111</v>
+      </c>
+      <c r="P23" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q23" s="43" t="str">
+        <f t="shared" ref="Q23:Q26" si="6">DEC2BIN(H23,8)</f>
+        <v>00001101</v>
+      </c>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+    </row>
+    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A24" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="50">
+        <f>_xlfn.BITAND(B23,B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="50">
+        <f>_xlfn.BITAND(D23,D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="50">
+        <f>_xlfn.BITAND(F23,F$4)</f>
+        <v>7</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" s="50">
+        <f>_xlfn.BITAND(H23,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="43" t="str">
+        <f t="shared" si="3"/>
+        <v>11000000</v>
+      </c>
+      <c r="L24" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="43" t="str">
+        <f t="shared" si="4"/>
+        <v>10101000</v>
+      </c>
+      <c r="N24" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O24" s="43" t="str">
+        <f t="shared" si="5"/>
+        <v>00000111</v>
+      </c>
+      <c r="P24" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q24" s="43" t="str">
+        <f t="shared" si="6"/>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="43">
+        <v>192</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="43">
+        <v>168</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="43">
+        <v>6</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" s="43">
+        <v>41</v>
+      </c>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="43" t="str">
+        <f t="shared" si="3"/>
+        <v>11000000</v>
+      </c>
+      <c r="L25" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="43" t="str">
+        <f t="shared" si="4"/>
+        <v>10101000</v>
+      </c>
+      <c r="N25" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O25" s="43" t="str">
+        <f t="shared" si="5"/>
+        <v>00000110</v>
+      </c>
+      <c r="P25" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q25" s="43" t="str">
+        <f t="shared" si="6"/>
+        <v>00101001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A26" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="50">
+        <f>_xlfn.BITAND(B25,B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="50">
+        <f>_xlfn.BITAND(D25,D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="50">
+        <f>_xlfn.BITAND(F25,F$4)</f>
+        <v>6</v>
+      </c>
+      <c r="G26" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" s="50">
+        <f>_xlfn.BITAND(H25,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="43" t="str">
+        <f t="shared" si="3"/>
+        <v>11000000</v>
+      </c>
+      <c r="L26" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="43" t="str">
+        <f t="shared" si="4"/>
+        <v>10101000</v>
+      </c>
+      <c r="N26" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O26" s="43" t="str">
+        <f t="shared" si="5"/>
+        <v>00000110</v>
+      </c>
+      <c r="P26" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q26" s="43" t="str">
+        <f t="shared" si="6"/>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A28" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="43">
+        <v>10</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="43">
+        <v>168</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="43">
+        <v>1</v>
+      </c>
+      <c r="G28" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" s="43">
+        <v>51</v>
+      </c>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="43" t="str">
+        <f t="shared" ref="K28:K33" si="7">DEC2BIN(B28,8)</f>
+        <v>00001010</v>
+      </c>
+      <c r="L28" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="43" t="str">
+        <f t="shared" ref="M28:M33" si="8">DEC2BIN(D28,8)</f>
+        <v>10101000</v>
+      </c>
+      <c r="N28" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O28" s="43" t="str">
+        <f t="shared" ref="O28:O33" si="9">DEC2BIN(F28,8)</f>
+        <v>00000001</v>
+      </c>
+      <c r="P28" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q28" s="43" t="str">
+        <f t="shared" ref="Q28:Q33" si="10">DEC2BIN(H28,8)</f>
+        <v>00110011</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A29" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="50">
+        <f>_xlfn.BITAND(B28,B$4)</f>
+        <v>10</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="50">
+        <f>_xlfn.BITAND(D28,D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="50">
+        <f>_xlfn.BITAND(F28,F$4)</f>
+        <v>1</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" s="50">
+        <f>_xlfn.BITAND(H28,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v>00001010</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>10101000</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O29" s="11" t="str">
+        <f t="shared" si="9"/>
+        <v>00000001</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q29" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="43">
+        <v>192</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="43">
+        <v>168</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="43">
+        <v>50</v>
+      </c>
+      <c r="G30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" s="43">
+        <v>23</v>
+      </c>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>11000000</v>
+      </c>
+      <c r="L30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="43" t="str">
+        <f t="shared" si="8"/>
+        <v>10101000</v>
+      </c>
+      <c r="N30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O30" s="43" t="str">
+        <f t="shared" si="9"/>
+        <v>00110010</v>
+      </c>
+      <c r="P30" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q30" s="43" t="str">
+        <f t="shared" si="10"/>
+        <v>00010111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A31" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="50">
+        <f>_xlfn.BITAND(B30,B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="50">
+        <f>_xlfn.BITAND(D30,D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E31" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="50">
+        <f>_xlfn.BITAND(F30,F$4)</f>
+        <v>50</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H31" s="50">
+        <f>_xlfn.BITAND(H30,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>11000000</v>
+      </c>
+      <c r="L31" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="43" t="str">
+        <f t="shared" si="8"/>
+        <v>10101000</v>
+      </c>
+      <c r="N31" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O31" s="43" t="str">
+        <f t="shared" si="9"/>
+        <v>00110010</v>
+      </c>
+      <c r="P31" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q31" s="43" t="str">
+        <f t="shared" si="10"/>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.4">
+      <c r="A32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="43">
+        <v>192</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="43">
+        <v>168</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="43">
+        <v>1</v>
+      </c>
+      <c r="G32" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" s="43">
+        <v>23</v>
+      </c>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>11000000</v>
+      </c>
+      <c r="L32" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="43" t="str">
+        <f t="shared" si="8"/>
+        <v>10101000</v>
+      </c>
+      <c r="N32" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O32" s="43" t="str">
+        <f t="shared" si="9"/>
+        <v>00000001</v>
+      </c>
+      <c r="P32" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q32" s="43" t="str">
+        <f t="shared" si="10"/>
+        <v>00010111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15" x14ac:dyDescent="0.4">
+      <c r="A33" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="50">
+        <f>_xlfn.BITAND(B32,B$4)</f>
+        <v>192</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="50">
+        <f>_xlfn.BITAND(D32,D$4)</f>
+        <v>168</v>
+      </c>
+      <c r="E33" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="50">
+        <f>_xlfn.BITAND(F32,F$4)</f>
+        <v>1</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" s="50">
+        <f>_xlfn.BITAND(H32,H$4)</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>11000000</v>
+      </c>
+      <c r="L33" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="43" t="str">
+        <f t="shared" si="8"/>
+        <v>10101000</v>
+      </c>
+      <c r="N33" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="O33" s="43" t="str">
+        <f t="shared" si="9"/>
+        <v>00000001</v>
+      </c>
+      <c r="P33" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q33" s="43" t="str">
+        <f t="shared" si="10"/>
+        <v>00000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B24:H24">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
+      <formula>B$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:H26">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="notEqual">
+      <formula>B$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29:H29">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
+      <formula>B$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:H31">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
+      <formula>B$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:H33">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
+      <formula>B$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/public/assets/excel_router_solution.xlsx
+++ b/public/assets/excel_router_solution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcc\git\informatikgarten.ch\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F6059B-5C28-4A34-A909-D724F5B28683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119D18B8-AA1F-4464-BA40-4B39E3A68C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="14220" activeTab="2" xr2:uid="{8B4C5CB2-983E-4FDC-89E4-8A1111F2665D}"/>
+    <workbookView minimized="1" xWindow="930" yWindow="2110" windowWidth="14180" windowHeight="11600" activeTab="1" xr2:uid="{8B4C5CB2-983E-4FDC-89E4-8A1111F2665D}"/>
   </bookViews>
   <sheets>
     <sheet name="Einstieg" sheetId="1" r:id="rId1"/>
@@ -1643,13 +1643,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>530413</xdr:colOff>
+      <xdr:colOff>530415</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>173868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>698510</xdr:colOff>
+      <xdr:colOff>610578</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>75595</xdr:rowOff>
     </xdr:to>
@@ -1666,10 +1666,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5754044" y="362856"/>
-          <a:ext cx="2443514" cy="5465537"/>
+          <a:off x="5761838" y="364368"/>
+          <a:ext cx="2371048" cy="5509265"/>
           <a:chOff x="5754044" y="362856"/>
-          <a:chExt cx="2443514" cy="5397501"/>
+          <a:chExt cx="2482335" cy="5397501"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -1685,8 +1685,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5835952" y="362856"/>
-            <a:ext cx="2281128" cy="5397501"/>
+            <a:off x="5835951" y="362856"/>
+            <a:ext cx="2400428" cy="5397501"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3614,10 +3614,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
@@ -5425,7 +5421,7 @@
         <v>255</v>
       </c>
       <c r="U10" s="11" t="str">
-        <f>DEC2BIN(T10,8)</f>
+        <f t="shared" ref="U10:U18" si="1">DEC2BIN(T10,8)</f>
         <v>11111111</v>
       </c>
       <c r="V10" s="11"/>
@@ -5492,7 +5488,7 @@
         <v>254</v>
       </c>
       <c r="U11" s="11" t="str">
-        <f>DEC2BIN(T11,8)</f>
+        <f t="shared" si="1"/>
         <v>11111110</v>
       </c>
       <c r="V11" s="11"/>
@@ -5520,7 +5516,7 @@
         <v>252</v>
       </c>
       <c r="U12" s="11" t="str">
-        <f>DEC2BIN(T12,8)</f>
+        <f t="shared" si="1"/>
         <v>11111100</v>
       </c>
       <c r="V12" s="11"/>
@@ -5549,7 +5545,7 @@
         <v>248</v>
       </c>
       <c r="U13" s="11" t="str">
-        <f>DEC2BIN(T13,8)</f>
+        <f t="shared" si="1"/>
         <v>11111000</v>
       </c>
     </row>
@@ -5575,7 +5571,7 @@
         <v>240</v>
       </c>
       <c r="U14" s="11" t="str">
-        <f>DEC2BIN(T14,8)</f>
+        <f t="shared" si="1"/>
         <v>11110000</v>
       </c>
     </row>
@@ -5641,7 +5637,7 @@
         <v>224</v>
       </c>
       <c r="U15" s="11" t="str">
-        <f>DEC2BIN(T15,8)</f>
+        <f t="shared" si="1"/>
         <v>11100000</v>
       </c>
     </row>
@@ -5707,7 +5703,7 @@
         <v>192</v>
       </c>
       <c r="U16" s="11" t="str">
-        <f>DEC2BIN(T16,8)</f>
+        <f t="shared" si="1"/>
         <v>11000000</v>
       </c>
     </row>
@@ -5773,7 +5769,7 @@
         <v>128</v>
       </c>
       <c r="U17" s="11" t="str">
-        <f>DEC2BIN(T17,8)</f>
+        <f t="shared" si="1"/>
         <v>10000000</v>
       </c>
     </row>
@@ -5782,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="11" t="str">
-        <f>DEC2BIN(T18,8)</f>
+        <f t="shared" si="1"/>
         <v>00000000</v>
       </c>
     </row>
@@ -5837,28 +5833,28 @@
         <v>39</v>
       </c>
       <c r="K21" s="46" t="str">
-        <f t="shared" ref="K21:K30" si="1">DEC2BIN(B21,8)</f>
+        <f t="shared" ref="K21:K30" si="2">DEC2BIN(B21,8)</f>
         <v>11000000</v>
       </c>
       <c r="L21" s="46" t="s">
         <v>57</v>
       </c>
       <c r="M21" s="46" t="str">
-        <f t="shared" ref="M21:M30" si="2">DEC2BIN(D21,8)</f>
+        <f t="shared" ref="M21:M30" si="3">DEC2BIN(D21,8)</f>
         <v>10101000</v>
       </c>
       <c r="N21" s="46" t="s">
         <v>57</v>
       </c>
       <c r="O21" s="46" t="str">
-        <f t="shared" ref="O21:O30" si="3">DEC2BIN(F21,8)</f>
+        <f t="shared" ref="O21:O30" si="4">DEC2BIN(F21,8)</f>
         <v>00000110</v>
       </c>
       <c r="P21" s="46" t="s">
         <v>57</v>
       </c>
       <c r="Q21" s="46" t="str">
-        <f t="shared" ref="Q21:Q30" si="4">DEC2BIN(H21,8)</f>
+        <f t="shared" ref="Q21:Q30" si="5">DEC2BIN(H21,8)</f>
         <v>00001101</v>
       </c>
     </row>
@@ -5892,28 +5888,28 @@
         <v>0</v>
       </c>
       <c r="K22" s="43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11000000</v>
       </c>
       <c r="L22" s="43" t="s">
         <v>57</v>
       </c>
       <c r="M22" s="43" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10101000</v>
       </c>
       <c r="N22" s="43" t="s">
         <v>57</v>
       </c>
       <c r="O22" s="43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>00000110</v>
       </c>
       <c r="P22" s="43" t="s">
         <v>57</v>
       </c>
       <c r="Q22" s="43" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>00000000</v>
       </c>
     </row>
@@ -5947,28 +5943,28 @@
         <v>39</v>
       </c>
       <c r="K23" s="46" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11000000</v>
       </c>
       <c r="L23" s="46" t="s">
         <v>57</v>
       </c>
       <c r="M23" s="46" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10101000</v>
       </c>
       <c r="N23" s="46" t="s">
         <v>57</v>
       </c>
       <c r="O23" s="46" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>00000111</v>
       </c>
       <c r="P23" s="46" t="s">
         <v>57</v>
       </c>
       <c r="Q23" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>00101001</v>
       </c>
     </row>
@@ -6004,28 +6000,28 @@
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24" s="43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11000000</v>
       </c>
       <c r="L24" s="43" t="s">
         <v>57</v>
       </c>
       <c r="M24" s="43" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10101000</v>
       </c>
       <c r="N24" s="43" t="s">
         <v>57</v>
       </c>
       <c r="O24" s="43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>00000110</v>
       </c>
       <c r="P24" s="43" t="s">
         <v>57</v>
       </c>
       <c r="Q24" s="43" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>00000000</v>
       </c>
     </row>
@@ -6171,28 +6167,28 @@
         <v>39</v>
       </c>
       <c r="K27" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>00001010</v>
       </c>
       <c r="L27" s="45" t="s">
         <v>57</v>
       </c>
       <c r="M27" s="45" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10101000</v>
       </c>
       <c r="N27" s="45" t="s">
         <v>57</v>
       </c>
       <c r="O27" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>00000001</v>
       </c>
       <c r="P27" s="45" t="s">
         <v>57</v>
       </c>
       <c r="Q27" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>00110011</v>
       </c>
     </row>
@@ -6228,28 +6224,28 @@
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>00001010</v>
       </c>
       <c r="L28" s="11" t="s">
         <v>57</v>
       </c>
       <c r="M28" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10101000</v>
       </c>
       <c r="N28" s="11" t="s">
         <v>57</v>
       </c>
       <c r="O28" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>00000000</v>
       </c>
       <c r="P28" s="11" t="s">
         <v>57</v>
       </c>
       <c r="Q28" s="11" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>00000000</v>
       </c>
       <c r="V28" s="11"/>
@@ -6285,28 +6281,28 @@
         <v>39</v>
       </c>
       <c r="K29" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11000000</v>
       </c>
       <c r="L29" s="45" t="s">
         <v>57</v>
       </c>
       <c r="M29" s="45" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10101000</v>
       </c>
       <c r="N29" s="45" t="s">
         <v>57</v>
       </c>
       <c r="O29" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>00110010</v>
       </c>
       <c r="P29" s="45" t="s">
         <v>57</v>
       </c>
       <c r="Q29" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>00010111</v>
       </c>
     </row>
@@ -6342,28 +6338,28 @@
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30" s="43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11000000</v>
       </c>
       <c r="L30" s="43" t="s">
         <v>57</v>
       </c>
       <c r="M30" s="43" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10101000</v>
       </c>
       <c r="N30" s="43" t="s">
         <v>57</v>
       </c>
       <c r="O30" s="43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>00110010</v>
       </c>
       <c r="P30" s="43" t="s">
         <v>57</v>
       </c>
       <c r="Q30" s="43" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>00000000</v>
       </c>
       <c r="S30"/>
@@ -6805,19 +6801,19 @@
         <v>0</v>
       </c>
       <c r="W18" s="58">
-        <f>IF(R8=R18,1,0)</f>
+        <f t="shared" ref="W18:Z19" si="1">IF(R8=R18,1,0)</f>
         <v>1</v>
       </c>
       <c r="X18" s="58">
-        <f>IF(S8=S18,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Y18" s="58">
-        <f>IF(T8=T18,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Z18" s="58">
-        <f>IF(U8=U18,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AA18" s="58">
@@ -6877,19 +6873,19 @@
         <v>0</v>
       </c>
       <c r="W19" s="59">
-        <f>IF(R9=R19,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X19" s="59">
-        <f>IF(S9=S19,1,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y19" s="59">
-        <f>IF(T9=T19,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Z19" s="59">
-        <f>IF(U9=U19,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AA19" s="59">
